--- a/artfynd/A 33668-2023 artfynd.xlsx
+++ b/artfynd/A 33668-2023 artfynd.xlsx
@@ -5737,10 +5737,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113188766</v>
+        <v>113188774</v>
       </c>
       <c r="B49" t="n">
-        <v>56910</v>
+        <v>90705</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5749,42 +5749,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>898</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>537428</v>
+        <v>537515</v>
       </c>
       <c r="R49" t="n">
-        <v>7202982</v>
+        <v>7202975</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5816,7 +5812,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5826,7 +5822,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5853,10 +5849,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113188774</v>
+        <v>113188766</v>
       </c>
       <c r="B50" t="n">
-        <v>90689</v>
+        <v>56910</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5865,38 +5861,42 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>898</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>537515</v>
+        <v>537428</v>
       </c>
       <c r="R50" t="n">
-        <v>7202975</v>
+        <v>7202982</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5928,7 +5928,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 33668-2023 artfynd.xlsx
+++ b/artfynd/A 33668-2023 artfynd.xlsx
@@ -5740,7 +5740,7 @@
         <v>113188774</v>
       </c>
       <c r="B49" t="n">
-        <v>90705</v>
+        <v>90717</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5852,7 +5852,7 @@
         <v>113188766</v>
       </c>
       <c r="B50" t="n">
-        <v>56910</v>
+        <v>56911</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>

--- a/artfynd/A 33668-2023 artfynd.xlsx
+++ b/artfynd/A 33668-2023 artfynd.xlsx
@@ -5737,10 +5737,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113188774</v>
+        <v>113188766</v>
       </c>
       <c r="B49" t="n">
-        <v>90717</v>
+        <v>56911</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5749,38 +5749,42 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>898</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>537515</v>
+        <v>537428</v>
       </c>
       <c r="R49" t="n">
-        <v>7202975</v>
+        <v>7202982</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5812,7 +5816,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5822,7 +5826,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5849,10 +5853,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113188766</v>
+        <v>113188774</v>
       </c>
       <c r="B50" t="n">
-        <v>56911</v>
+        <v>90717</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5861,42 +5865,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>898</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>537428</v>
+        <v>537515</v>
       </c>
       <c r="R50" t="n">
-        <v>7202982</v>
+        <v>7202975</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5928,7 +5928,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 33668-2023 artfynd.xlsx
+++ b/artfynd/A 33668-2023 artfynd.xlsx
@@ -5856,7 +5856,7 @@
         <v>113188774</v>
       </c>
       <c r="B50" t="n">
-        <v>90717</v>
+        <v>90739</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>

--- a/artfynd/A 33668-2023 artfynd.xlsx
+++ b/artfynd/A 33668-2023 artfynd.xlsx
@@ -5740,7 +5740,7 @@
         <v>113188766</v>
       </c>
       <c r="B49" t="n">
-        <v>56911</v>
+        <v>56914</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
         <v>113188774</v>
       </c>
       <c r="B50" t="n">
-        <v>90739</v>
+        <v>90743</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>

--- a/artfynd/A 33668-2023 artfynd.xlsx
+++ b/artfynd/A 33668-2023 artfynd.xlsx
@@ -5740,7 +5740,7 @@
         <v>113188766</v>
       </c>
       <c r="B49" t="n">
-        <v>56914</v>
+        <v>56918</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
         <v>113188774</v>
       </c>
       <c r="B50" t="n">
-        <v>90743</v>
+        <v>90749</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>

--- a/artfynd/A 33668-2023 artfynd.xlsx
+++ b/artfynd/A 33668-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
